--- a/ALLY_LOTTE_WH/DATA/0627_棧板資訊_含入庫單號.xlsx
+++ b/ALLY_LOTTE_WH/DATA/0627_棧板資訊_含入庫單號.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K445"/>
+  <dimension ref="A1:M445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,16 @@
           <t>ean</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>alloc_batch_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>alloc_timestamp</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -521,6 +531,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>BATCH_00001</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -570,6 +590,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>BATCH_00002</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -619,6 +649,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BATCH_00003</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -668,6 +708,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>BATCH_00004</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -717,6 +767,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>BATCH_00005</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -766,6 +826,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>BATCH_00006</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -815,6 +885,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>BATCH_00007</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -864,6 +944,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>BATCH_00008</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -913,6 +1003,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>BATCH_00009</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -962,6 +1062,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>BATCH_00010</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1011,6 +1121,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>BATCH_00011</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1060,6 +1180,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BATCH_00012</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1109,6 +1239,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>BATCH_00013</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1158,6 +1298,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>BATCH_00014</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1207,6 +1357,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>BATCH_00015</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1256,6 +1416,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>BATCH_00016</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1305,6 +1475,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>BATCH_00017</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1354,6 +1534,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>BATCH_00018</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1403,6 +1593,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>BATCH_00019</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1452,6 +1652,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BATCH_00020</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1501,6 +1711,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BATCH_00021</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1550,6 +1770,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BATCH_00022</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1599,6 +1829,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BATCH_00023</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1648,6 +1888,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>BATCH_00024</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1697,6 +1947,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>BATCH_00025</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1746,6 +2006,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>BATCH_00026</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1795,6 +2065,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>BATCH_00027</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1844,6 +2124,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>BATCH_00028</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1893,6 +2183,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>BATCH_00029</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1942,6 +2242,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>BATCH_00030</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1991,6 +2301,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>BATCH_00031</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2040,6 +2360,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>BATCH_00032</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2089,6 +2419,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>BATCH_00033</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2138,6 +2478,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>BATCH_00034</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2187,6 +2537,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>BATCH_00035</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2236,6 +2596,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>BATCH_00036</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2285,6 +2655,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>BATCH_00037</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2334,6 +2714,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>BATCH_00038</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2383,6 +2773,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>BATCH_00039</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2432,6 +2832,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>BATCH_00040</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2481,6 +2891,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>BATCH_00041</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2530,6 +2950,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>BATCH_00042</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2579,6 +3009,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>BATCH_00043</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2628,6 +3068,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>BATCH_00044</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2677,6 +3127,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>BATCH_00045</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2726,6 +3186,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>BATCH_00046</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2775,6 +3245,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>BATCH_00047</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2824,6 +3304,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>BATCH_00048</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2873,6 +3363,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>BATCH_00049</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2922,6 +3422,16 @@
           <t>58852008304867</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>BATCH_00050</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2971,6 +3481,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>BATCH_00051</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3020,6 +3540,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>BATCH_00052</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3069,6 +3599,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>BATCH_00053</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3118,6 +3658,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>BATCH_00054</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3167,6 +3717,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>BATCH_00055</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3216,6 +3776,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>BATCH_00056</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3265,6 +3835,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>BATCH_00057</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3314,6 +3894,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>BATCH_00058</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3363,6 +3953,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>BATCH_00059</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3412,6 +4012,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>BATCH_00060</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3461,6 +4071,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>BATCH_00061</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3510,6 +4130,16 @@
           <t>58852008304911</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>BATCH_00062</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3559,6 +4189,16 @@
           <t>58852008305390</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>BATCH_00063</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3608,6 +4248,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>BATCH_00064</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3657,6 +4307,16 @@
           <t>58852008304911</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>BATCH_00065</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3706,6 +4366,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>BATCH_00066</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3755,6 +4425,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>BATCH_00067</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3804,6 +4484,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>BATCH_00068</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3853,6 +4543,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>BATCH_00069</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3902,6 +4602,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>BATCH_00070</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3951,6 +4661,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>BATCH_00071</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4000,6 +4720,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>BATCH_00072</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4049,6 +4779,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>BATCH_00073</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4098,6 +4838,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>BATCH_00074</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4147,6 +4897,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>BATCH_00075</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4196,6 +4956,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>BATCH_00076</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4245,6 +5015,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>BATCH_00077</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4294,6 +5074,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>BATCH_00078</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4343,6 +5133,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>BATCH_00079</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4392,6 +5192,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>BATCH_00080</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4441,6 +5251,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>BATCH_00081</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4490,6 +5310,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>BATCH_00082</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4539,6 +5369,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>BATCH_00083</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4588,6 +5428,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>BATCH_00084</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4637,6 +5487,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>BATCH_00085</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4686,6 +5546,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>BATCH_00086</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4735,6 +5605,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>BATCH_00087</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4784,6 +5664,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>BATCH_00088</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4833,6 +5723,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>BATCH_00089</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4882,6 +5782,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>BATCH_00090</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4931,6 +5841,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>BATCH_00091</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4980,6 +5900,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>BATCH_00092</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5029,6 +5959,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>BATCH_00093</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5078,6 +6018,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>BATCH_00094</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5127,6 +6077,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>BATCH_00095</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5176,6 +6136,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>BATCH_00096</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5225,6 +6195,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>BATCH_00097</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5274,6 +6254,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>BATCH_00098</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5323,6 +6313,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>BATCH_00099</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5372,6 +6372,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>BATCH_00100</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5421,6 +6431,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>BATCH_00101</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5470,6 +6490,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>BATCH_00102</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5519,6 +6549,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>BATCH_00103</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5568,6 +6608,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>BATCH_00104</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5617,6 +6667,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>BATCH_00105</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5666,6 +6726,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>BATCH_00106</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5715,6 +6785,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>BATCH_00107</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5764,6 +6844,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>BATCH_00108</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5813,6 +6903,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>BATCH_00109</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5862,6 +6962,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>BATCH_00110</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5911,6 +7021,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>BATCH_00111</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5960,6 +7080,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>BATCH_00112</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6009,6 +7139,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>BATCH_00113</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6058,6 +7198,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>BATCH_00114</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6107,6 +7257,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>BATCH_00115</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6156,6 +7316,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>BATCH_00116</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6205,6 +7375,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>BATCH_00117</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6254,6 +7434,16 @@
           <t>14712834455187</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>BATCH_00118</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6303,6 +7493,16 @@
           <t>14712834455187</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>BATCH_00119</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6352,6 +7552,16 @@
           <t>14712834455187</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>BATCH_00120</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6401,6 +7611,16 @@
           <t>14712834455187</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>BATCH_00121</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6450,6 +7670,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>BATCH_00122</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6499,6 +7729,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>BATCH_00123</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6548,6 +7788,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>BATCH_00124</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6597,6 +7847,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>BATCH_00125</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6646,6 +7906,16 @@
           <t>04712834457153</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>BATCH_00126</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6695,6 +7965,16 @@
           <t>0712834457160</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>BATCH_00127</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6740,6 +8020,16 @@
           <t>4712834457344</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>PENDING_00001</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6789,6 +8079,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>BATCH_00128</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6838,6 +8138,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>BATCH_00129</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6887,6 +8197,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>BATCH_00130</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6936,6 +8256,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>BATCH_00131</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6985,6 +8315,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>BATCH_00132</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7034,6 +8374,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>BATCH_00133</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7083,6 +8433,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>BATCH_00134</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7132,6 +8492,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>BATCH_00135</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7181,6 +8551,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>BATCH_00136</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7230,6 +8610,16 @@
           <t>18801062899613</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>BATCH_00137</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7279,6 +8669,16 @@
           <t>18801062899613</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>BATCH_00138</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7328,6 +8728,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>BATCH_00139</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7377,6 +8787,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>BATCH_00140</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7426,6 +8846,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>BATCH_00141</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7475,6 +8905,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>BATCH_00142</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7524,6 +8964,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>BATCH_00143</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7573,6 +9023,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>BATCH_00144</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7622,6 +9082,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>BATCH_00145</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7671,6 +9141,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>BATCH_00146</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7720,6 +9200,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>BATCH_00147</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7769,6 +9259,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>BATCH_00148</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7818,6 +9318,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>BATCH_00149</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7867,6 +9377,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>BATCH_00150</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7916,6 +9436,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>BATCH_00151</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7965,6 +9495,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>BATCH_00152</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8014,6 +9554,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>BATCH_00153</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8063,6 +9613,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>BATCH_00154</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8112,6 +9672,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>BATCH_00155</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8161,6 +9731,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>BATCH_00156</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8206,6 +9786,16 @@
           <t>0712834457160</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>PENDING_00002</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8251,6 +9841,16 @@
           <t>0712834457160</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>PENDING_00003</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8296,6 +9896,16 @@
           <t>0712834457160</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>PENDING_00004</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8345,6 +9955,16 @@
           <t>0712834457160</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>BATCH_00157</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8394,6 +10014,16 @@
           <t>18801062000781</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>BATCH_00158</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8443,6 +10073,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>BATCH_00159</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8492,6 +10132,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>BATCH_00160</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8541,6 +10191,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>BATCH_00161</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8590,6 +10250,16 @@
           <t>8935341300736</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>BATCH_00162</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8639,6 +10309,16 @@
           <t>8935341300736</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>BATCH_00163</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8688,6 +10368,16 @@
           <t>08935341301337</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>BATCH_00164</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8737,6 +10427,16 @@
           <t>08935341301337</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>BATCH_00165</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8786,6 +10486,16 @@
           <t>08935341301337</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>BATCH_00166</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8835,6 +10545,16 @@
           <t>08935341301337</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>BATCH_00167</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8884,6 +10604,16 @@
           <t>08935341301337</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>BATCH_00168</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8933,6 +10663,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>BATCH_00169</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8982,6 +10722,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>BATCH_00170</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9031,6 +10781,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>BATCH_00171</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9080,6 +10840,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>BATCH_00172</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9129,6 +10899,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>BATCH_00173</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9178,6 +10958,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>BATCH_00174</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9227,6 +11017,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>BATCH_00175</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9276,6 +11076,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>BATCH_00176</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9325,6 +11135,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>BATCH_00177</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9374,6 +11194,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>BATCH_00178</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9423,6 +11253,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>BATCH_00179</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9472,6 +11312,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>BATCH_00180</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9521,6 +11371,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>BATCH_00181</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9570,6 +11430,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>BATCH_00182</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9619,6 +11489,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>BATCH_00183</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9668,6 +11548,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>BATCH_00184</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9717,6 +11607,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>BATCH_00185</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9766,6 +11666,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>BATCH_00186</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9815,6 +11725,16 @@
           <t>8935341301832</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>BATCH_00187</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9864,6 +11784,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>BATCH_00188</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9913,6 +11843,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>BATCH_00189</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9958,6 +11898,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>PENDING_00005</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10007,6 +11957,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>BATCH_00190</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10056,6 +12016,16 @@
           <t>18801062899613</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>BATCH_00191</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10105,6 +12075,16 @@
           <t>18801062899613</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>BATCH_00192</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10154,6 +12134,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>BATCH_00193</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10203,6 +12193,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>BATCH_00194</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10248,6 +12248,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>PENDING_00006</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10293,6 +12303,16 @@
           <t>18801062006202</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>PENDING_00007</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10338,6 +12358,16 @@
           <t>18801062000781</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>PENDING_00008</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10387,6 +12417,16 @@
           <t>18801062000781</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>BATCH_00195</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10436,6 +12476,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>BATCH_00196</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10485,6 +12535,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>BATCH_00197</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10534,6 +12594,16 @@
           <t>58852008510053</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>BATCH_00198</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10583,6 +12653,16 @@
           <t>8935341301832</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>BATCH_00199</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10632,6 +12712,16 @@
           <t>14903333256812</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>BATCH_00200</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10681,6 +12771,16 @@
           <t>38801062221975</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>BATCH_00201</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10730,6 +12830,16 @@
           <t>38801062221197</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>BATCH_00202</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10779,6 +12889,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>BATCH_00203</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10828,6 +12948,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>BATCH_00204</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10877,6 +13007,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>BATCH_00205</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10926,6 +13066,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>BATCH_00206</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10975,6 +13125,16 @@
           <t>38801062221975</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>BATCH_00207</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11024,6 +13184,16 @@
           <t>58801062332255</t>
         </is>
       </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>BATCH_00208</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11073,6 +13243,16 @@
           <t>38801062335610</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>BATCH_00209</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11122,6 +13302,16 @@
           <t>38801062335610</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>BATCH_00210</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11171,6 +13361,16 @@
           <t>38801062479925</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>BATCH_00211</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11220,6 +13420,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>BATCH_00212</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11269,6 +13479,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>BATCH_00213</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11318,6 +13538,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>BATCH_00214</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11367,6 +13597,16 @@
           <t>14712834455118</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>BATCH_00215</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11416,6 +13656,16 @@
           <t>14712834455118</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>BATCH_00216</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11465,6 +13715,16 @@
           <t>04712834455166</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>BATCH_00217</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11514,6 +13774,16 @@
           <t>04712834455166</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>BATCH_00218</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11563,6 +13833,16 @@
           <t>14712834455187</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>BATCH_00219</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11612,6 +13892,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>BATCH_00220</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11661,6 +13951,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>BATCH_00221</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11710,6 +14010,16 @@
           <t>04712834457153</t>
         </is>
       </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>BATCH_00222</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11759,6 +14069,16 @@
           <t>08934677004912</t>
         </is>
       </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>BATCH_00223</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11808,6 +14128,16 @@
           <t>08934677004936</t>
         </is>
       </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>BATCH_00224</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11857,6 +14187,16 @@
           <t>08934677004929</t>
         </is>
       </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>BATCH_00225</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11906,6 +14246,16 @@
           <t>14903333226129</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>BATCH_00226</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11955,6 +14305,16 @@
           <t>14903333226129</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>BATCH_00227</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12004,6 +14364,16 @@
           <t>14903333226129</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>BATCH_00228</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12049,6 +14419,16 @@
           <t>14903333257451</t>
         </is>
       </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>PENDING_00009</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12094,6 +14474,16 @@
           <t>14903333207142</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>PENDING_00010</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12143,6 +14533,16 @@
           <t>14903333207142</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>BATCH_00229</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12188,6 +14588,16 @@
           <t>48801062161889</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>PENDING_00011</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -12237,6 +14647,16 @@
           <t>18801062126221</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>BATCH_00230</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -12286,6 +14706,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>BATCH_00231</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -12331,6 +14761,16 @@
           <t>18801062865687</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>PENDING_00012</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12376,6 +14816,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>PENDING_00013</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12425,6 +14875,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>BATCH_00232</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12474,6 +14934,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>BATCH_00233</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12523,6 +14993,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>BATCH_00234</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12572,6 +15052,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>BATCH_00235</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -12621,6 +15111,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>BATCH_00236</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -12670,6 +15170,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>BATCH_00237</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12719,6 +15229,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>BATCH_00238</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12768,6 +15288,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>BATCH_00239</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12813,6 +15343,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>PENDING_00014</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12862,6 +15402,16 @@
           <t>58852008304867</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>BATCH_00240</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12911,6 +15461,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>BATCH_00241</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -12956,6 +15516,16 @@
           <t>58852008300265</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>PENDING_00015</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13001,6 +15571,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>PENDING_00016</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13050,6 +15630,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>BATCH_00242</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13099,6 +15689,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>BATCH_00243</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -13148,6 +15748,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>BATCH_00244</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -13197,6 +15807,16 @@
           <t>58852008304911</t>
         </is>
       </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>BATCH_00245</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -13246,6 +15866,16 @@
           <t>58852008305413</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>BATCH_00246</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -13295,6 +15925,16 @@
           <t>58852008305673</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>BATCH_00247</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -13344,6 +15984,16 @@
           <t>58852008300265</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>BATCH_00248</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -13393,6 +16043,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>BATCH_00249</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -13438,6 +16098,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>PENDING_00017</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -13487,6 +16157,16 @@
           <t>58852008304911</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>BATCH_00250</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13536,6 +16216,16 @@
           <t>58852008304935</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>BATCH_00251</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -13585,6 +16275,16 @@
           <t>58852008305390</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>BATCH_00252</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -13634,6 +16334,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>BATCH_00253</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -13683,6 +16393,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>BATCH_00254</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13732,6 +16452,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>BATCH_00255</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13781,6 +16511,16 @@
           <t>58852008510053</t>
         </is>
       </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>BATCH_00256</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -13830,6 +16570,16 @@
           <t>58852008510510</t>
         </is>
       </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>BATCH_00257</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -13879,6 +16629,16 @@
           <t>58852008510510</t>
         </is>
       </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>BATCH_00258</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -13928,6 +16688,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>BATCH_00259</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -13977,6 +16747,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>BATCH_00260</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14026,6 +16806,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>BATCH_00261</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14075,6 +16865,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>BATCH_00262</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14124,6 +16924,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>BATCH_00263</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14173,6 +16983,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>BATCH_00264</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14222,6 +17042,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>BATCH_00265</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14271,6 +17101,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>BATCH_00266</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14316,6 +17156,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>PENDING_00018</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14361,6 +17211,16 @@
           <t>18801062633460</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>PENDING_00019</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14410,6 +17270,16 @@
           <t>18801062633460</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>BATCH_00267</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14459,6 +17329,16 @@
           <t>18801062633460</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>BATCH_00268</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14504,6 +17384,16 @@
           <t>14903333270665</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>PENDING_00020</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -14549,6 +17439,16 @@
           <t>34903333219835</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>PENDING_00021</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14598,6 +17498,16 @@
           <t>14903333256812</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>BATCH_00269</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -14643,6 +17553,16 @@
           <t>68801062332115</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>PENDING_00022</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -14692,6 +17612,16 @@
           <t>68801062332115</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>BATCH_00270</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -14741,6 +17671,16 @@
           <t>68801062332115</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>BATCH_00271</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -14790,6 +17730,16 @@
           <t>38801062221975</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>BATCH_00272</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -14839,6 +17789,16 @@
           <t>38801062221975</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>BATCH_00273</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -14888,6 +17848,16 @@
           <t>38801062221975</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>BATCH_00274</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -14937,6 +17907,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>BATCH_00275</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -14986,6 +17966,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>BATCH_00276</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15035,6 +18025,16 @@
           <t>38801062221197</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>BATCH_00277</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -15084,6 +18084,16 @@
           <t>38801062221197</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>BATCH_00278</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -15129,6 +18139,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>PENDING_00023</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -15174,6 +18194,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>PENDING_00024</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -15223,6 +18253,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>BATCH_00279</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -15272,6 +18312,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>BATCH_00280</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -15321,6 +18371,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>BATCH_00281</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -15366,6 +18426,16 @@
           <t>04712834457320</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>PENDING_00025</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -15411,6 +18481,16 @@
           <t>4712834457344</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>PENDING_00026</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -15460,6 +18540,16 @@
           <t>04712834457429</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>BATCH_00282</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -15497,6 +18587,16 @@
       </c>
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>PENDING_00027</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -15542,6 +18642,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -15587,6 +18697,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -15632,6 +18752,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -15677,6 +18807,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -15722,6 +18862,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -15767,6 +18917,16 @@
           <t>18801062865717</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -15812,6 +18972,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -15857,6 +19027,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -15902,6 +19082,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -15947,6 +19137,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -15992,6 +19192,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -16037,6 +19247,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -16082,6 +19302,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -16127,6 +19357,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -16172,6 +19412,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -16217,6 +19467,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -16262,6 +19522,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -16307,6 +19577,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -16352,6 +19632,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -16397,6 +19687,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -16442,6 +19742,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -16487,6 +19797,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -16532,6 +19852,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -16577,6 +19907,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -16622,6 +19962,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -16667,6 +20017,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -16712,6 +20072,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -16757,6 +20127,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -16802,6 +20182,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -16847,6 +20237,16 @@
           <t>18801062132765</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -16892,6 +20292,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -16937,6 +20347,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -16982,6 +20402,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -17027,6 +20457,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -17072,6 +20512,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -17117,6 +20567,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -17162,6 +20622,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -17207,6 +20677,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -17252,6 +20732,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -17297,6 +20787,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -17342,6 +20842,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -17387,6 +20897,16 @@
           <t>28801062481730</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -17432,6 +20952,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -17477,6 +21007,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -17522,6 +21062,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -17567,6 +21117,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -17612,6 +21172,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -17657,6 +21227,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -17702,6 +21282,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -17747,6 +21337,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -17792,6 +21392,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -17837,6 +21447,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -17882,6 +21502,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -17927,6 +21557,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -17972,6 +21612,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -18017,6 +21667,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -18062,6 +21722,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -18107,6 +21777,16 @@
           <t>18801062881748</t>
         </is>
       </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -18152,6 +21832,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -18197,6 +21887,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -18242,6 +21942,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -18287,6 +21997,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -18332,6 +22052,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -18377,6 +22107,16 @@
           <t>18801062132765</t>
         </is>
       </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -18422,6 +22162,16 @@
           <t>18801062132765</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -18467,6 +22217,16 @@
           <t>18801062132765</t>
         </is>
       </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -18512,6 +22272,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -18557,6 +22327,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -18602,6 +22382,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -18647,6 +22437,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -18692,6 +22492,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -18737,6 +22547,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -18782,6 +22602,16 @@
           <t>18801062126481</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -18827,6 +22657,16 @@
           <t>18801062126481</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -18872,6 +22712,16 @@
           <t>18801062126481</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -18917,6 +22767,16 @@
           <t>18801062126481</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -18962,6 +22822,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -19007,6 +22877,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -19052,6 +22932,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -19097,6 +22987,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -19142,6 +23042,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -19187,6 +23097,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -19232,6 +23152,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -19277,6 +23207,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -19322,6 +23262,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -19367,6 +23317,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -19412,6 +23372,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -19457,6 +23427,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -19502,6 +23482,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -19547,6 +23537,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -19592,6 +23592,16 @@
           <t>28801062481730</t>
         </is>
       </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -19637,6 +23647,16 @@
           <t>48801062016097</t>
         </is>
       </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -19682,6 +23702,16 @@
           <t>48801062016097</t>
         </is>
       </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -19727,6 +23757,16 @@
           <t>48801062016097</t>
         </is>
       </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -19772,6 +23812,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -19817,6 +23867,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -19862,6 +23922,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -19907,6 +23977,16 @@
           <t>18801062881748</t>
         </is>
       </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -19952,6 +24032,16 @@
           <t>18801062880147</t>
         </is>
       </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -19997,6 +24087,16 @@
           <t>18801062880147</t>
         </is>
       </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -20042,6 +24142,16 @@
           <t>48801062016097</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -20087,6 +24197,16 @@
           <t>48801062016097</t>
         </is>
       </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -20132,6 +24252,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -20177,6 +24307,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -20222,6 +24362,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -20267,6 +24417,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -20312,6 +24472,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -20357,6 +24527,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -20402,6 +24582,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -20447,6 +24637,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -20492,6 +24692,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -20537,6 +24747,16 @@
           <t>18801062865717</t>
         </is>
       </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -20582,6 +24802,16 @@
           <t>18801062132765</t>
         </is>
       </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -20627,6 +24857,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -20672,6 +24912,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -20717,6 +24967,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -20762,6 +25022,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -20807,6 +25077,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -20852,6 +25132,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -20897,6 +25187,16 @@
           <t>18801062126481</t>
         </is>
       </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -20942,6 +25242,16 @@
           <t>28801062481730</t>
         </is>
       </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -20987,6 +25297,16 @@
           <t>28801062481730</t>
         </is>
       </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -21032,6 +25352,16 @@
           <t>18801062881748</t>
         </is>
       </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -21077,6 +25407,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -21122,6 +25462,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -21167,6 +25517,16 @@
           <t>28801062481730</t>
         </is>
       </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -21212,6 +25572,16 @@
           <t>18801062860521</t>
         </is>
       </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -21257,6 +25627,16 @@
           <t>18801062860521</t>
         </is>
       </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -21302,6 +25682,16 @@
           <t>18801062016096</t>
         </is>
       </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -21347,6 +25737,16 @@
           <t>28801062482201</t>
         </is>
       </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -21392,6 +25792,16 @@
           <t>68801062479834</t>
         </is>
       </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -21437,6 +25847,16 @@
           <t>14903333258847</t>
         </is>
       </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -21482,6 +25902,16 @@
           <t>14903333220448</t>
         </is>
       </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -21527,6 +25957,16 @@
           <t>44903333248733</t>
         </is>
       </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -21570,6 +26010,16 @@
       <c r="K445" t="inlineStr">
         <is>
           <t>44903333207235</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
         </is>
       </c>
     </row>
